--- a/utils/monday_sprint_sprint_2025-13.xlsx
+++ b/utils/monday_sprint_sprint_2025-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1370" uniqueCount="260">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1369" uniqueCount="261">
   <si>
     <t>Ticket</t>
   </si>
@@ -189,7 +189,7 @@
     <t>25/04/2023</t>
   </si>
   <si>
-    <t>23/02/2026</t>
+    <t>18/02/2026</t>
   </si>
   <si>
     <t>Semana 4</t>
@@ -213,7 +213,7 @@
     <t>30/05/2025</t>
   </si>
   <si>
-    <t>14/03/2026</t>
+    <t>09/03/2026</t>
   </si>
   <si>
     <t>Implantação</t>
@@ -249,6 +249,9 @@
     <t>31/01/2025</t>
   </si>
   <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
     <t>Janeiro</t>
   </si>
   <si>
@@ -639,7 +642,7 @@
     <t>13/06/2025</t>
   </si>
   <si>
-    <t>11/03/2026</t>
+    <t>06/03/2026</t>
   </si>
   <si>
     <t>Planilha - Controle de OSs - Instalação Industrial</t>
@@ -2049,7 +2052,7 @@
         <v>77</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="L19" s="2" t="s">
         <v>32</v>
@@ -2058,12 +2061,12 @@
         <v>68</v>
       </c>
       <c r="N19" s="2" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>15</v>
@@ -2075,10 +2078,10 @@
         <v>52</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>19</v>
@@ -2090,7 +2093,7 @@
         <v>56</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="K20" s="2" t="s">
         <v>17</v>
@@ -2107,7 +2110,7 @@
     </row>
     <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>15</v>
@@ -2119,10 +2122,10 @@
         <v>17</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>19</v>
@@ -2151,7 +2154,7 @@
     </row>
     <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>15</v>
@@ -2163,10 +2166,10 @@
         <v>17</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>19</v>
@@ -2195,7 +2198,7 @@
     </row>
     <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>15</v>
@@ -2207,10 +2210,10 @@
         <v>17</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>19</v>
@@ -2239,7 +2242,7 @@
     </row>
     <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>15</v>
@@ -2251,10 +2254,10 @@
         <v>17</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>19</v>
@@ -2283,7 +2286,7 @@
     </row>
     <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>15</v>
@@ -2295,10 +2298,10 @@
         <v>17</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>19</v>
@@ -2327,7 +2330,7 @@
     </row>
     <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>15</v>
@@ -2339,10 +2342,10 @@
         <v>17</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>19</v>
@@ -2363,7 +2366,7 @@
         <v>20</v>
       </c>
       <c r="M26" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N26" s="2" t="s">
         <v>17</v>
@@ -2371,7 +2374,7 @@
     </row>
     <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>15</v>
@@ -2383,13 +2386,13 @@
         <v>52</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H27" s="2" t="s">
         <v>75</v>
@@ -2398,24 +2401,24 @@
         <v>76</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="K27" s="2" t="s">
         <v>17</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M27" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>15</v>
@@ -2427,13 +2430,13 @@
         <v>17</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>17</v>
@@ -2451,7 +2454,7 @@
         <v>67</v>
       </c>
       <c r="M28" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N28" s="2" t="s">
         <v>17</v>
@@ -2459,7 +2462,7 @@
     </row>
     <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>15</v>
@@ -2471,10 +2474,10 @@
         <v>17</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>19</v>
@@ -2492,10 +2495,10 @@
         <v>17</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N29" s="2" t="s">
         <v>17</v>
@@ -2503,7 +2506,7 @@
     </row>
     <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>15</v>
@@ -2515,10 +2518,10 @@
         <v>17</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>19</v>
@@ -2547,7 +2550,7 @@
     </row>
     <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>15</v>
@@ -2559,10 +2562,10 @@
         <v>17</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>19</v>
@@ -2591,7 +2594,7 @@
     </row>
     <row r="32" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>15</v>
@@ -2603,13 +2606,13 @@
         <v>17</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>17</v>
@@ -2635,7 +2638,7 @@
     </row>
     <row r="33" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>15</v>
@@ -2647,10 +2650,10 @@
         <v>17</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>19</v>
@@ -2671,7 +2674,7 @@
         <v>32</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N33" s="2" t="s">
         <v>17</v>
@@ -2679,7 +2682,7 @@
     </row>
     <row r="34" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>15</v>
@@ -2691,10 +2694,10 @@
         <v>17</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>19</v>
@@ -2723,7 +2726,7 @@
     </row>
     <row r="35" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>15</v>
@@ -2735,10 +2738,10 @@
         <v>17</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>19</v>
@@ -2779,10 +2782,10 @@
         <v>17</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>19</v>
@@ -2823,10 +2826,10 @@
         <v>17</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>19</v>
@@ -2855,7 +2858,7 @@
     </row>
     <row r="38" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>15</v>
@@ -2867,10 +2870,10 @@
         <v>17</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>19</v>
@@ -2899,7 +2902,7 @@
     </row>
     <row r="39" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>15</v>
@@ -2911,10 +2914,10 @@
         <v>17</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>19</v>
@@ -2943,7 +2946,7 @@
     </row>
     <row r="40" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>15</v>
@@ -2955,10 +2958,10 @@
         <v>17</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>19</v>
@@ -2987,7 +2990,7 @@
     </row>
     <row r="41" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>15</v>
@@ -2999,10 +3002,10 @@
         <v>17</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>19</v>
@@ -3031,7 +3034,7 @@
     </row>
     <row r="42" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>15</v>
@@ -3043,10 +3046,10 @@
         <v>17</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>19</v>
@@ -3075,7 +3078,7 @@
     </row>
     <row r="43" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>15</v>
@@ -3087,13 +3090,13 @@
         <v>17</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>17</v>
@@ -3119,7 +3122,7 @@
     </row>
     <row r="44" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>15</v>
@@ -3131,10 +3134,10 @@
         <v>17</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>19</v>
@@ -3163,7 +3166,7 @@
     </row>
     <row r="45" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>15</v>
@@ -3175,39 +3178,39 @@
         <v>52</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="I45" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="L45" s="2" t="s">
         <v>32</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="46" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>15</v>
@@ -3219,10 +3222,10 @@
         <v>17</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F46" s="2" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="G46" s="2" t="s">
         <v>19</v>
@@ -3251,7 +3254,7 @@
     </row>
     <row r="47" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>15</v>
@@ -3263,10 +3266,10 @@
         <v>17</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>19</v>
@@ -3295,7 +3298,7 @@
     </row>
     <row r="48" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>15</v>
@@ -3307,10 +3310,10 @@
         <v>17</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>19</v>
@@ -3339,7 +3342,7 @@
     </row>
     <row r="49" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>15</v>
@@ -3351,10 +3354,10 @@
         <v>17</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>19</v>
@@ -3383,7 +3386,7 @@
     </row>
     <row r="50" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>15</v>
@@ -3395,10 +3398,10 @@
         <v>17</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>19</v>
@@ -3427,7 +3430,7 @@
     </row>
     <row r="51" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>15</v>
@@ -3439,10 +3442,10 @@
         <v>17</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>19</v>
@@ -3471,7 +3474,7 @@
     </row>
     <row r="52" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>15</v>
@@ -3483,10 +3486,10 @@
         <v>17</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>19</v>
@@ -3515,7 +3518,7 @@
     </row>
     <row r="53" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>15</v>
@@ -3527,10 +3530,10 @@
         <v>17</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>19</v>
@@ -3559,7 +3562,7 @@
     </row>
     <row r="54" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>15</v>
@@ -3571,10 +3574,10 @@
         <v>17</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>19</v>
@@ -3603,7 +3606,7 @@
     </row>
     <row r="55" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>15</v>
@@ -3615,13 +3618,13 @@
         <v>17</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>17</v>
@@ -3636,7 +3639,7 @@
         <v>17</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M55" s="2" t="s">
         <v>21</v>
@@ -3647,7 +3650,7 @@
     </row>
     <row r="56" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>15</v>
@@ -3659,10 +3662,10 @@
         <v>17</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>19</v>
@@ -3691,7 +3694,7 @@
     </row>
     <row r="57" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>15</v>
@@ -3703,10 +3706,10 @@
         <v>17</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>19</v>
@@ -3735,7 +3738,7 @@
     </row>
     <row r="58" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>15</v>
@@ -3747,10 +3750,10 @@
         <v>17</v>
       </c>
       <c r="E58" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F58" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="G58" s="2" t="s">
         <v>19</v>
@@ -3779,7 +3782,7 @@
     </row>
     <row r="59" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>15</v>
@@ -3791,10 +3794,10 @@
         <v>17</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>19</v>
@@ -3823,7 +3826,7 @@
     </row>
     <row r="60" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>15</v>
@@ -3835,10 +3838,10 @@
         <v>17</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>19</v>
@@ -3867,7 +3870,7 @@
     </row>
     <row r="61" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>15</v>
@@ -3879,13 +3882,13 @@
         <v>17</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>17</v>
@@ -3911,7 +3914,7 @@
     </row>
     <row r="62" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>15</v>
@@ -3923,10 +3926,10 @@
         <v>17</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>19</v>
@@ -3944,7 +3947,7 @@
         <v>17</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="M62" s="2" t="s">
         <v>26</v>
@@ -3955,7 +3958,7 @@
     </row>
     <row r="63" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>15</v>
@@ -3967,10 +3970,10 @@
         <v>17</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>19</v>
@@ -3999,7 +4002,7 @@
     </row>
     <row r="64" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>15</v>
@@ -4011,10 +4014,10 @@
         <v>17</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>19</v>
@@ -4043,7 +4046,7 @@
     </row>
     <row r="65" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>15</v>
@@ -4055,10 +4058,10 @@
         <v>17</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>19</v>
@@ -4087,7 +4090,7 @@
     </row>
     <row r="66" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>15</v>
@@ -4099,10 +4102,10 @@
         <v>17</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>19</v>
@@ -4131,7 +4134,7 @@
     </row>
     <row r="67" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>15</v>
@@ -4143,10 +4146,10 @@
         <v>17</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>19</v>
@@ -4175,7 +4178,7 @@
     </row>
     <row r="68" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>15</v>
@@ -4187,13 +4190,13 @@
         <v>17</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>17</v>
@@ -4219,7 +4222,7 @@
     </row>
     <row r="69" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>15</v>
@@ -4231,25 +4234,25 @@
         <v>52</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="I69" s="2" t="s">
         <v>56</v>
       </c>
       <c r="J69" s="2" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>20</v>
@@ -4258,12 +4261,12 @@
         <v>26</v>
       </c>
       <c r="N69" s="2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
     </row>
     <row r="70" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>15</v>
@@ -4275,10 +4278,10 @@
         <v>17</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>19</v>
@@ -4307,7 +4310,7 @@
     </row>
     <row r="71" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>15</v>
@@ -4319,13 +4322,13 @@
         <v>17</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>17</v>
@@ -4351,7 +4354,7 @@
     </row>
     <row r="72" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>15</v>
@@ -4363,10 +4366,10 @@
         <v>17</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>19</v>
@@ -4395,7 +4398,7 @@
     </row>
     <row r="73" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>199</v>
+        <v>200</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>15</v>
@@ -4407,10 +4410,10 @@
         <v>17</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>200</v>
+        <v>201</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>19</v>
@@ -4439,7 +4442,7 @@
     </row>
     <row r="74" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>15</v>
@@ -4451,10 +4454,10 @@
         <v>17</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>19</v>
@@ -4483,7 +4486,7 @@
     </row>
     <row r="75" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>15</v>
@@ -4495,25 +4498,25 @@
         <v>52</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>19</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="I75" s="2" t="s">
         <v>76</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>20</v>
@@ -4522,12 +4525,12 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
     </row>
     <row r="76" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>15</v>
@@ -4539,10 +4542,10 @@
         <v>17</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>19</v>
@@ -4571,7 +4574,7 @@
     </row>
     <row r="77" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>15</v>
@@ -4583,13 +4586,13 @@
         <v>17</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>17</v>
@@ -4615,7 +4618,7 @@
     </row>
     <row r="78" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>15</v>
@@ -4627,10 +4630,10 @@
         <v>17</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>19</v>
@@ -4659,7 +4662,7 @@
     </row>
     <row r="79" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>15</v>
@@ -4671,10 +4674,10 @@
         <v>17</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>19</v>
@@ -4703,7 +4706,7 @@
     </row>
     <row r="80" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>15</v>
@@ -4715,10 +4718,10 @@
         <v>17</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>19</v>
@@ -4736,7 +4739,7 @@
         <v>17</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="M80" s="2" t="s">
         <v>21</v>
@@ -4747,7 +4750,7 @@
     </row>
     <row r="81" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="B81" s="2" t="s">
         <v>15</v>
@@ -4759,10 +4762,10 @@
         <v>17</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>19</v>
@@ -4791,7 +4794,7 @@
     </row>
     <row r="82" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>15</v>
@@ -4803,10 +4806,10 @@
         <v>17</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>19</v>
@@ -4835,7 +4838,7 @@
     </row>
     <row r="83" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>15</v>
@@ -4847,10 +4850,10 @@
         <v>17</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>19</v>
@@ -4879,7 +4882,7 @@
     </row>
     <row r="84" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>15</v>
@@ -4891,10 +4894,10 @@
         <v>17</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>19</v>
@@ -4923,7 +4926,7 @@
     </row>
     <row r="85" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>15</v>
@@ -4935,10 +4938,10 @@
         <v>17</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>19</v>
@@ -4967,7 +4970,7 @@
     </row>
     <row r="86" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>15</v>
@@ -4979,10 +4982,10 @@
         <v>17</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>19</v>
@@ -5011,7 +5014,7 @@
     </row>
     <row r="87" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>15</v>
@@ -5023,10 +5026,10 @@
         <v>17</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>19</v>
@@ -5055,7 +5058,7 @@
     </row>
     <row r="88" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>15</v>
@@ -5067,10 +5070,10 @@
         <v>17</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>19</v>
@@ -5099,7 +5102,7 @@
     </row>
     <row r="89" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>15</v>
@@ -5111,10 +5114,10 @@
         <v>17</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>19</v>
@@ -5143,7 +5146,7 @@
     </row>
     <row r="90" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>15</v>
@@ -5155,10 +5158,10 @@
         <v>17</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>19</v>
@@ -5187,7 +5190,7 @@
     </row>
     <row r="91" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>15</v>
@@ -5199,10 +5202,10 @@
         <v>17</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>19</v>
@@ -5231,7 +5234,7 @@
     </row>
     <row r="92" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>15</v>
@@ -5243,10 +5246,10 @@
         <v>17</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>19</v>
@@ -5286,23 +5289,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="B2" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="D2" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="E2" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5310,16 +5313,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5338,7 +5341,7 @@
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5359,7 +5362,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5390,12 +5393,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="B2">
         <v>91</v>
@@ -5419,25 +5422,25 @@
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5454,13 +5457,13 @@
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5472,10 +5475,10 @@
         <v>64</v>
       </c>
       <c r="P10" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="Q10">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="11" spans="4:17" x14ac:dyDescent="0.25">
@@ -5486,13 +5489,13 @@
         <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="H11">
         <v>10</v>
       </c>
       <c r="J11" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="K11">
         <v>91</v>
@@ -5507,7 +5510,7 @@
         <v>26</v>
       </c>
       <c r="Q11">
-        <v>33</v>
+        <v>31</v>
       </c>
     </row>
     <row r="12" spans="4:17" x14ac:dyDescent="0.25">
@@ -5524,7 +5527,7 @@
         <v>81</v>
       </c>
       <c r="M12" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N12">
         <v>2</v>
@@ -5533,7 +5536,7 @@
         <v>21</v>
       </c>
       <c r="Q12">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="13" spans="4:17" x14ac:dyDescent="0.25">
@@ -5544,7 +5547,7 @@
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H13">
         <v>0</v>
@@ -5556,15 +5559,15 @@
         <v>4</v>
       </c>
       <c r="P13" t="s">
-        <v>59</v>
+        <v>68</v>
       </c>
       <c r="Q13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="7:17" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
       <c r="G14" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H14">
         <v>0</v>
@@ -5575,16 +5578,10 @@
       <c r="N14">
         <v>6</v>
       </c>
-      <c r="P14" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q14">
-        <v>3</v>
-      </c>
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -5592,7 +5589,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5600,7 +5597,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5608,7 +5605,7 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
     </row>
     <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
@@ -5619,7 +5616,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5633,7 +5630,7 @@
         <v>15</v>
       </c>
       <c r="F21" s="2">
-        <v>1020</v>
+        <v>1015</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>53</v>
@@ -5647,7 +5644,7 @@
         <v>15</v>
       </c>
       <c r="F22" s="2">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>73</v>
@@ -5655,58 +5652,58 @@
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>188</v>
+        <v>97</v>
       </c>
       <c r="E23" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F23" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>189</v>
+        <v>98</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>96</v>
+        <v>189</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F24" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>97</v>
+        <v>190</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F25" s="2">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E26" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F26" s="2">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
@@ -5717,7 +5714,7 @@
         <v>15</v>
       </c>
       <c r="F27" s="2">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="G27" s="2" t="s">
         <v>62</v>
@@ -5725,16 +5722,16 @@
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="E28" s="2" t="s">
         <v>15</v>
       </c>
       <c r="F28" s="2">
-        <v>256</v>
+        <v>251</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">

--- a/utils/monday_sprint_sprint_2025-13.xlsx
+++ b/utils/monday_sprint_sprint_2025-13.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1463" uniqueCount="264">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1465" uniqueCount="285">
   <si>
     <t>Ticket</t>
   </si>
@@ -42,7 +42,7 @@
     <t>Equipe TI</t>
   </si>
   <si>
-    <t>Entrada Sprint</t>
+    <t>Abertura</t>
   </si>
   <si>
     <t>Encerramento</t>
@@ -51,7 +51,7 @@
     <t>Status</t>
   </si>
   <si>
-    <t>SLA (15 dias)</t>
+    <t>Dentro da SLA</t>
   </si>
   <si>
     <t>Semana</t>
@@ -60,7 +60,7 @@
     <t>Mês</t>
   </si>
   <si>
-    <t>30903</t>
+    <t>9382021959</t>
   </si>
   <si>
     <t>Setor não informado</t>
@@ -87,7 +87,7 @@
     <t>16/06/2025</t>
   </si>
   <si>
-    <t>N/A</t>
+    <t>23/06/2025</t>
   </si>
   <si>
     <t>Feito</t>
@@ -102,10 +102,16 @@
     <t>Junho</t>
   </si>
   <si>
+    <t>9382022104</t>
+  </si>
+  <si>
     <t>Cadastro do tipo de anexos.</t>
   </si>
   <si>
-    <t>32045</t>
+    <t>24/06/2025</t>
+  </si>
+  <si>
+    <t>9374840587</t>
   </si>
   <si>
     <t>Melhoria</t>
@@ -117,16 +123,19 @@
     <t>13/06/2025</t>
   </si>
   <si>
+    <t>19/06/2025</t>
+  </si>
+  <si>
     <t>Semana 2</t>
   </si>
   <si>
-    <t>31233</t>
+    <t>9382200281</t>
   </si>
   <si>
     <t>Integração faturamento x Benner  Reunião de entrega</t>
   </si>
   <si>
-    <t>32287</t>
+    <t>9372879863</t>
   </si>
   <si>
     <t>Projeto</t>
@@ -135,13 +144,13 @@
     <t>Aplicação de controle de consumo e custo de PROEX e Antecipação de Caterpillar - Reunião</t>
   </si>
   <si>
+    <t>15/06/2025</t>
+  </si>
+  <si>
     <t>A fazer</t>
   </si>
   <si>
-    <t>Aberto</t>
-  </si>
-  <si>
-    <t>32048</t>
+    <t>9374854817</t>
   </si>
   <si>
     <t>Correção</t>
@@ -150,430 +159,460 @@
     <t>Base QVD de Recibo de Embarque com Erro</t>
   </si>
   <si>
-    <t>31977</t>
+    <t>9382233272</t>
   </si>
   <si>
     <t>Alterações no registro de moldagem via APP</t>
   </si>
   <si>
+    <t>9382022318</t>
+  </si>
+  <si>
     <t>Cadastro de declarações.</t>
   </si>
   <si>
-    <t>30796</t>
+    <t>9382206838</t>
   </si>
   <si>
     <t>Sistema gestão de ações</t>
   </si>
   <si>
-    <t>32144</t>
+    <t>9374436786</t>
   </si>
   <si>
     <t>Sistema de Radiografia automática em amostras</t>
   </si>
   <si>
+    <t>28/06/2025</t>
+  </si>
+  <si>
+    <t>9382022207</t>
+  </si>
+  <si>
     <t>Cadastro parâmetros de declarações.</t>
   </si>
   <si>
-    <t>32148</t>
+    <t>9373327814</t>
   </si>
   <si>
     <t>Pendência compras</t>
   </si>
   <si>
-    <t>32077</t>
+    <t>17/06/2025</t>
+  </si>
+  <si>
+    <t>9374748106</t>
   </si>
   <si>
     <t>alterar informações de romaneio e quantidade</t>
   </si>
   <si>
-    <t>31529</t>
+    <t>9382185586</t>
   </si>
   <si>
     <t>Pré-lista em cascata, por endereço</t>
   </si>
   <si>
+    <t>25/06/2025</t>
+  </si>
+  <si>
     <t>Fazendo</t>
   </si>
   <si>
-    <t>19909</t>
+    <t>9382021576</t>
   </si>
   <si>
     <t>Consulta Registros</t>
   </si>
   <si>
-    <t>32022</t>
+    <t>9281415938</t>
+  </si>
+  <si>
+    <t>Gerar registro na APON3 e MDL_TempoSeq dos apontamentos dos robôs Dalka e Lianco</t>
+  </si>
+  <si>
+    <t>02/06/2025</t>
+  </si>
+  <si>
+    <t>26/06/2025</t>
+  </si>
+  <si>
+    <t>Implantação</t>
+  </si>
+  <si>
+    <t>Semana 1</t>
+  </si>
+  <si>
+    <t>9170502510</t>
+  </si>
+  <si>
+    <t>Atualizar códigos de paradas UPR - Analisar</t>
+  </si>
+  <si>
+    <t>16/05/2025</t>
+  </si>
+  <si>
+    <t>Maio</t>
+  </si>
+  <si>
+    <t>29853</t>
+  </si>
+  <si>
+    <t>Logística</t>
   </si>
   <si>
     <t>Solicitação de serviço</t>
   </si>
   <si>
-    <t>Gerar registro na APON3 e MDL_TempoSeq dos apontamentos dos robôs Dalka e Lianco</t>
-  </si>
-  <si>
-    <t>Boa tarde! Abrindo chamado referente ao desenvolvimento do sistema de apontamentos via CLP das células de rebarbação automatizadas. Atenciosamente,</t>
-  </si>
-  <si>
-    <t>Leonardo Barbosa de Moraes</t>
+    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
+  </si>
+  <si>
+    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
+  </si>
+  <si>
+    <t>Djalma Machado</t>
+  </si>
+  <si>
+    <t>ADH</t>
+  </si>
+  <si>
+    <t>19/05/2026</t>
+  </si>
+  <si>
+    <t>9270488161</t>
+  </si>
+  <si>
+    <t>Melhoria WMS - Conferencia e Carregamento</t>
+  </si>
+  <si>
+    <t>30/05/2025</t>
+  </si>
+  <si>
+    <t>Semana 5</t>
+  </si>
+  <si>
+    <t>9382233168</t>
+  </si>
+  <si>
+    <t>Etiquetas corpo de prova</t>
+  </si>
+  <si>
+    <t>9373009208</t>
+  </si>
+  <si>
+    <t>Ajuste de Sistema - Criação/Alteração de Sequências</t>
+  </si>
+  <si>
+    <t>9382233500</t>
+  </si>
+  <si>
+    <t>Relatório de comissões por invoice por período e representante</t>
+  </si>
+  <si>
+    <t>29/06/2025</t>
+  </si>
+  <si>
+    <t>9372894143</t>
+  </si>
+  <si>
+    <t>Ajustar a baixa de oferta quando foi perdida/cancelada e Alterar os relatórios de Orçamentos Cancelados e Perdid</t>
+  </si>
+  <si>
+    <t>9382233354</t>
+  </si>
+  <si>
+    <t>Registro e relatório de liquido penetrante</t>
+  </si>
+  <si>
+    <t>9312379520</t>
+  </si>
+  <si>
+    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
+  </si>
+  <si>
+    <t>05/06/2025</t>
+  </si>
+  <si>
+    <t>30069</t>
+  </si>
+  <si>
+    <t>Sistema de Controle de Importação - Definição de contas</t>
+  </si>
+  <si>
+    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
+  </si>
+  <si>
+    <t>Alta</t>
+  </si>
+  <si>
+    <t>Impedimento</t>
+  </si>
+  <si>
+    <t>9279890653</t>
+  </si>
+  <si>
+    <t>Sistema tablet acabamento linhas UPR</t>
+  </si>
+  <si>
+    <t>20/06/2025</t>
+  </si>
+  <si>
+    <t>9310176039</t>
+  </si>
+  <si>
+    <t>Rateio de tempo padrão acabamento</t>
+  </si>
+  <si>
+    <t>Homologação</t>
+  </si>
+  <si>
+    <t>9374773312</t>
+  </si>
+  <si>
+    <t>Modo de falha</t>
+  </si>
+  <si>
+    <t>9372952900</t>
+  </si>
+  <si>
+    <t>Atualização apontamento eletrônico manipuladores</t>
+  </si>
+  <si>
+    <t>9372993245</t>
+  </si>
+  <si>
+    <t>Ações Deutsche Bahn</t>
+  </si>
+  <si>
+    <t>9322272584</t>
+  </si>
+  <si>
+    <t>Informação do percentual de refugo por motivo pela quantidade produzida no QlickSense</t>
+  </si>
+  <si>
+    <t>06/06/2025</t>
+  </si>
+  <si>
+    <t>9373431906</t>
+  </si>
+  <si>
+    <t>Altona || Relatório para controle das compras de consignados</t>
+  </si>
+  <si>
+    <t>9382233589</t>
+  </si>
+  <si>
+    <t>Máquina de Ensaios</t>
+  </si>
+  <si>
+    <t>9382022434</t>
+  </si>
+  <si>
+    <t>Controle de acesso.</t>
+  </si>
+  <si>
+    <t>9382022547</t>
+  </si>
+  <si>
+    <t>Controle do status por declaração</t>
+  </si>
+  <si>
+    <t>9382041838</t>
+  </si>
+  <si>
+    <t>Apresentação Faseamento Reunião</t>
+  </si>
+  <si>
+    <t>9374876459</t>
+  </si>
+  <si>
+    <t>Informações SIC/Nimbi</t>
+  </si>
+  <si>
+    <t>9374917153</t>
+  </si>
+  <si>
+    <t>Atualização de Gerência por Setor com Vigência Histórica no Script das Aplicações</t>
+  </si>
+  <si>
+    <t>22/06/2025</t>
+  </si>
+  <si>
+    <t>9372930930</t>
+  </si>
+  <si>
+    <t>Inventário Itens Grupo 30 (Compra Spot)</t>
+  </si>
+  <si>
+    <t>9382092448</t>
+  </si>
+  <si>
+    <t>Diário do bordo Ajustagem - Leitura de Tempo por Cabine</t>
+  </si>
+  <si>
+    <t>9271009275</t>
+  </si>
+  <si>
+    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
+  </si>
+  <si>
+    <t>9382130258</t>
+  </si>
+  <si>
+    <t>Apontamento Quebra de Canal - Reunião</t>
+  </si>
+  <si>
+    <t>32133</t>
+  </si>
+  <si>
+    <t>Comercial</t>
+  </si>
+  <si>
+    <t>Automatização planilha comercial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
+  </si>
+  <si>
+    <t>Jacson Schneider Movidesk</t>
   </si>
   <si>
     <t>Sistemas</t>
   </si>
   <si>
-    <t>02/06/2025</t>
-  </si>
-  <si>
-    <t>09/03/2026</t>
-  </si>
-  <si>
-    <t>Implantação</t>
-  </si>
-  <si>
-    <t>Semana 1</t>
-  </si>
-  <si>
-    <t>31511</t>
-  </si>
-  <si>
-    <t>Atualizar códigos de paradas UPR - Analisar</t>
-  </si>
-  <si>
-    <t>16/05/2025</t>
-  </si>
-  <si>
-    <t>Maio</t>
-  </si>
-  <si>
-    <t>29853</t>
-  </si>
-  <si>
-    <t>WMS - Sistema de Picking - Distribuição de Estoque em carteira</t>
-  </si>
-  <si>
-    <t>Boa tarde Conforme conversamos, precisamos de um sistema dentro do WMS que faça a distribuição em tempo real do saldo do Estoque com a carteira. Conforme é realizado o faturamento, a carteira seja atualizada em tempo real, bem como a entrada e estorno do material. O sistema deve fornecer um relatóri</t>
-  </si>
-  <si>
-    <t>Djalma Machado</t>
-  </si>
-  <si>
-    <t>ADH</t>
-  </si>
-  <si>
-    <t>19/05/2026</t>
-  </si>
-  <si>
-    <t>31836</t>
-  </si>
-  <si>
-    <t>Melhoria WMS - Conferencia e Carregamento</t>
-  </si>
-  <si>
-    <t>30/05/2025</t>
-  </si>
-  <si>
-    <t>Semana 5</t>
-  </si>
-  <si>
-    <t>31092</t>
-  </si>
-  <si>
-    <t>Etiquetas corpo de prova</t>
-  </si>
-  <si>
-    <t>32257</t>
-  </si>
-  <si>
-    <t>Ajuste de Sistema - Criação/Alteração de Sequências</t>
-  </si>
-  <si>
-    <t>31615</t>
-  </si>
-  <si>
-    <t>Relatório de comissões por invoice por período e representante</t>
-  </si>
-  <si>
-    <t>32271</t>
-  </si>
-  <si>
-    <t>Ajustar a baixa de oferta quando foi perdida/cancelada e Alterar os relatórios de Orçamentos Cancelados e Perdid</t>
-  </si>
-  <si>
-    <t>31827</t>
-  </si>
-  <si>
-    <t>Registro e relatório de liquido penetrante</t>
-  </si>
-  <si>
-    <t>29476</t>
-  </si>
-  <si>
-    <t>Qlik Sense - Dados Parcelas Invoice e Pgto</t>
-  </si>
-  <si>
-    <t>05/06/2025</t>
-  </si>
-  <si>
-    <t>30069</t>
-  </si>
-  <si>
-    <t>Sistema de Controle de Importação - Definição de contas</t>
-  </si>
-  <si>
-    <t>Boa tarde Vou assumir a importação da empresa e gostaria de criar um sistema de controle das Importações: Escopo principal: * Tela com todos as OC para importação - Liberação de Suprimentos para Logistica * Cadastro de processo (informações direto da OC) * Cadastro e controle de datas de embarques (</t>
-  </si>
-  <si>
-    <t>Alta</t>
-  </si>
-  <si>
-    <t>Impedimento</t>
-  </si>
-  <si>
-    <t>31520</t>
-  </si>
-  <si>
-    <t>Sistema tablet acabamento linhas UPR</t>
-  </si>
-  <si>
-    <t>9310176039</t>
-  </si>
-  <si>
-    <t>Rateio de tempo padrão acabamento</t>
-  </si>
-  <si>
-    <t>Homologação</t>
-  </si>
-  <si>
-    <t>32068</t>
-  </si>
-  <si>
-    <t>Modo de falha</t>
-  </si>
-  <si>
-    <t>32265</t>
-  </si>
-  <si>
-    <t>Atualização apontamento eletrônico manipuladores</t>
-  </si>
-  <si>
-    <t>32261</t>
-  </si>
-  <si>
-    <t>Ações Deutsche Bahn</t>
-  </si>
-  <si>
-    <t>30606</t>
-  </si>
-  <si>
-    <t>Informação do percentual de refugo por motivo pela quantidade produzida no QlickSense</t>
-  </si>
-  <si>
-    <t>06/06/2025</t>
-  </si>
-  <si>
-    <t>32146</t>
-  </si>
-  <si>
-    <t>Altona || Relatório para controle das compras de consignados</t>
-  </si>
-  <si>
-    <t>31257</t>
-  </si>
-  <si>
-    <t>Máquina de Ensaios</t>
-  </si>
-  <si>
-    <t>Controle de acesso.</t>
-  </si>
-  <si>
-    <t>Controle do status por declaração</t>
-  </si>
-  <si>
-    <t>25807</t>
-  </si>
-  <si>
-    <t>Apresentação Faseamento Reunião</t>
-  </si>
-  <si>
-    <t>32044</t>
-  </si>
-  <si>
-    <t>Informações SIC/Nimbi</t>
-  </si>
-  <si>
-    <t>32012</t>
-  </si>
-  <si>
-    <t>Atualização de Gerência por Setor com Vigência Histórica no Script das Aplicações</t>
-  </si>
-  <si>
-    <t>32267</t>
-  </si>
-  <si>
-    <t>Inventário Itens Grupo 30 (Compra Spot)</t>
-  </si>
-  <si>
-    <t>29095</t>
-  </si>
-  <si>
-    <t>Diário do bordo Ajustagem - Leitura de Tempo por Cabine</t>
-  </si>
-  <si>
-    <t>31699</t>
-  </si>
-  <si>
-    <t>Copiloto Gerencial IA - Descrição das Tabelas</t>
-  </si>
-  <si>
-    <t>9382130258</t>
-  </si>
-  <si>
-    <t>Apontamento Quebra de Canal - Reunião</t>
-  </si>
-  <si>
-    <t>32133</t>
-  </si>
-  <si>
-    <t>Automatização planilha comercial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bom dia Edson, Precisamos automatizar a planilha em Excel que usamos hoje para alimentar as informações de vendas realizadas, 80% de possibilidade de vendas e 50% de possibilidade de vendas. Essa automatização pode ser com base no programa usado para o Scrum, porém com um layout comercial. Segue em </t>
-  </si>
-  <si>
-    <t>Jacson Schneider Movidesk</t>
-  </si>
-  <si>
-    <t>32250</t>
+    <t>9373029910</t>
   </si>
   <si>
     <t>APONTAMENTO ELETRONICO JATO</t>
   </si>
   <si>
-    <t>32217</t>
+    <t>9373060634</t>
   </si>
   <si>
     <t>Trava - Lançamento de Datas</t>
   </si>
   <si>
-    <t>32200</t>
+    <t>9373098458</t>
   </si>
   <si>
     <t>Reabrir: Qlik Sense - Custos de Venda Geral</t>
   </si>
   <si>
-    <t>32224</t>
+    <t>9373043674</t>
   </si>
   <si>
     <t>Melhoria no sistema de corridas da Aciaria</t>
   </si>
   <si>
-    <t>32122</t>
+    <t>9374565098</t>
   </si>
   <si>
     <t>Altona || Melhoria relatório - WCONEXP1 - Planilha de Consumo de Materiais por valor</t>
   </si>
   <si>
-    <t>32132</t>
+    <t>9374548128</t>
   </si>
   <si>
     <t>P Number Solar - refugo</t>
   </si>
   <si>
-    <t>32002</t>
+    <t>9382249726</t>
   </si>
   <si>
     <t>Apontamento IROG-BI moldagem USE</t>
   </si>
   <si>
-    <t>30019</t>
+    <t>9382249621</t>
   </si>
   <si>
     <t>Peças em carteira - Ultimo fornecimento +4 anos</t>
   </si>
   <si>
-    <t>26428</t>
+    <t>9374967862</t>
   </si>
   <si>
     <t>CONSULTA EMBARQUES ALTONA</t>
   </si>
   <si>
-    <t>31835</t>
+    <t>9382249995</t>
   </si>
   <si>
     <t>computador de apontamento rebarbação VI</t>
   </si>
   <si>
-    <t>32177</t>
+    <t>9373165825</t>
   </si>
   <si>
     <t>Alterações na tela de inventario</t>
   </si>
   <si>
-    <t>32009</t>
+    <t>9374930847</t>
   </si>
   <si>
     <t>Relatório de modelos - quantidade de caixas de machos</t>
   </si>
   <si>
-    <t>32171</t>
+    <t>9373193607</t>
   </si>
   <si>
     <t>AJUSTES NO LAYOUT DE TELA DE TRABALHO APONTAMENTO ELETRONICO JATO</t>
   </si>
   <si>
-    <t>32197</t>
+    <t>9373131316</t>
   </si>
   <si>
     <t>Ajuste da Data de Abertura ID no QVD da CPC5742</t>
   </si>
   <si>
-    <t>30705</t>
+    <t>9374983666</t>
   </si>
   <si>
     <t>Montagem de Conjunto de Itens Comerciais</t>
   </si>
   <si>
-    <t>32158</t>
+    <t>9373206123</t>
   </si>
   <si>
     <t>L Number - prog moldagem vs exclusão</t>
   </si>
   <si>
-    <t>32037</t>
+    <t>9374900279</t>
   </si>
   <si>
     <t>BI ajustagem</t>
   </si>
   <si>
-    <t>31015</t>
+    <t>9382134705</t>
   </si>
   <si>
     <t>Conversão KB TOTO</t>
   </si>
   <si>
-    <t>31892</t>
+    <t>9382249866</t>
   </si>
   <si>
     <t>FORMULÁRIO GERAL DE ANÁLISE CRÍTICA</t>
   </si>
   <si>
-    <t>23838</t>
+    <t>9382146180</t>
   </si>
   <si>
     <t>Verificar a existência do CT-e na base altona</t>
   </si>
   <si>
-    <t>31292</t>
+    <t>9382138403</t>
   </si>
   <si>
     <t>Apontamento eletrônico corte pó de ferro  - Reunião</t>
   </si>
   <si>
-    <t>32281</t>
+    <t>9375068226</t>
   </si>
   <si>
     <t>Alteração no SMI</t>
   </si>
   <si>
-    <t>32298</t>
+    <t>9375047163</t>
   </si>
   <si>
     <t>Mapeamento Digital</t>
@@ -582,6 +621,9 @@
     <t>30012</t>
   </si>
   <si>
+    <t>PCP</t>
+  </si>
+  <si>
     <t>Saneamento de dados para APS e treinamento</t>
   </si>
   <si>
@@ -591,73 +633,67 @@
     <t>João Pedro Beccon</t>
   </si>
   <si>
-    <t>32113</t>
+    <t>9382405019</t>
   </si>
   <si>
     <t>Planilha - Controle de OSs - Instalação Industrial - Importar Planilha</t>
   </si>
   <si>
-    <t>31702</t>
+    <t>9382178687</t>
   </si>
   <si>
     <t>Migração de licenças para SAAS - Licença Supervisores</t>
   </si>
   <si>
-    <t>32119</t>
+    <t>9374619626</t>
   </si>
   <si>
     <t>Razão Crítica - Correção de Data de Tratamento Térmico</t>
   </si>
   <si>
-    <t>32239</t>
+    <t>9375133142</t>
   </si>
   <si>
     <t>ACRESCENTAR DUAS ETAPAS NO APONTAMENTO ELETRONICO/ MOTIVOS DE PARADAS</t>
   </si>
   <si>
-    <t>32107</t>
+    <t>9374666079</t>
   </si>
   <si>
     <t>Melhoria Controle de Refratario</t>
   </si>
   <si>
-    <t>32296</t>
-  </si>
-  <si>
-    <t>Fundição</t>
+    <t>9375057908</t>
   </si>
   <si>
     <t>Lista dos modelos e seu tempos padrões definidos</t>
   </si>
   <si>
-    <t>Boa tarde, Preciso da lista com todos os modelos que já possuem tempo padrão definido para as linhas (Carrossel e Fast Loop), será necessário revisar os tempos de alguns modelo. Att.</t>
-  </si>
-  <si>
-    <t>Matheus Rodrigues de Almeida</t>
-  </si>
-  <si>
-    <t>06/03/2026</t>
+    <t>9374629160</t>
   </si>
   <si>
     <t>Planilha - Controle de OSs - Instalação Industrial</t>
   </si>
   <si>
+    <t>9382427202</t>
+  </si>
+  <si>
     <t>Mapeamento de Solda</t>
   </si>
   <si>
-    <t>31682</t>
+    <t>9382178767</t>
   </si>
   <si>
     <t>Revisão de Pontos</t>
   </si>
   <si>
-    <t>24746</t>
+    <t>9382185283</t>
   </si>
   <si>
     <t>Integração de faturamentos com eventos</t>
   </si>
   <si>
-    <t>28583</t>
+    <t>9382178905</t>
   </si>
   <si>
     <t>Compara Carteira UPR - Erro</t>
@@ -666,6 +702,9 @@
     <t>32094</t>
   </si>
   <si>
+    <t>Manutenção</t>
+  </si>
+  <si>
     <t>implementar indicadores no sistema de manutenção</t>
   </si>
   <si>
@@ -678,34 +717,55 @@
     <t>27/05/2026</t>
   </si>
   <si>
+    <t>9397855398</t>
+  </si>
+  <si>
     <t>Incluir "Todos" no combo "Tipo de pátio"</t>
   </si>
   <si>
-    <t>17/06/2025</t>
+    <t>9397861973</t>
   </si>
   <si>
     <t>Permitir entrega de fornecedores de Blumenau sem CTe</t>
   </si>
   <si>
+    <t>9397868581</t>
+  </si>
+  <si>
     <t>Pedir numero da NF para fornecedores de Blumenau</t>
   </si>
   <si>
+    <t>9397872453</t>
+  </si>
+  <si>
     <t>Alterar Label de "Enviar arquivo " para "Enviar XML</t>
   </si>
   <si>
+    <t>9397884703</t>
+  </si>
+  <si>
     <t>Gerar evento no calendário a partir da criação da Ordem de coleta</t>
   </si>
   <si>
+    <t>9397888385</t>
+  </si>
+  <si>
     <t>Permitir gerar ordem de coleta apenas com o código do cliente e observaçoes</t>
   </si>
   <si>
+    <t>9397891715</t>
+  </si>
+  <si>
     <t>Possibilidade de eventos recorrentes - Funcionalidade para reservar horário para cliente</t>
   </si>
   <si>
+    <t>9397894725</t>
+  </si>
+  <si>
     <t>Bloqueio de calendário para inventário</t>
   </si>
   <si>
-    <t>32097</t>
+    <t>9402197033</t>
   </si>
   <si>
     <t>ERRO NA GERAÇÃO DA OFERTA</t>
@@ -714,13 +774,13 @@
     <t>18/06/2025</t>
   </si>
   <si>
-    <t>31688</t>
+    <t>9270709943</t>
   </si>
   <si>
     <t>Qlik - Relação de NF com OTF que não entram no Faturamento</t>
   </si>
   <si>
-    <t>31841</t>
+    <t>9270467413</t>
   </si>
   <si>
     <t>Atualização de QVD Romaneio</t>
@@ -732,7 +792,7 @@
     <t>Período</t>
   </si>
   <si>
-    <t>SPRINT 2025-13</t>
+    <t>Mai/2025</t>
   </si>
   <si>
     <t>Base</t>
@@ -784,6 +844,9 @@
   </si>
   <si>
     <t>Sim</t>
+  </si>
+  <si>
+    <t>Semana 4</t>
   </si>
   <si>
     <t>Abertos</t>
@@ -1335,7 +1398,7 @@
     </row>
     <row r="3" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>16</v>
@@ -1347,10 +1410,10 @@
         <v>18</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="G3" s="2" t="s">
         <v>20</v>
@@ -1365,7 +1428,7 @@
         <v>23</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>25</v>
@@ -1382,22 +1445,22 @@
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D4" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="G4" s="2" t="s">
         <v>20</v>
@@ -1409,10 +1472,10 @@
         <v>22</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L4" s="2" t="s">
         <v>25</v>
@@ -1421,7 +1484,7 @@
         <v>26</v>
       </c>
       <c r="N4" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O4" s="2" t="s">
         <v>28</v>
@@ -1429,22 +1492,22 @@
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D5" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="G5" s="2" t="s">
         <v>20</v>
@@ -1459,7 +1522,7 @@
         <v>23</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L5" s="2" t="s">
         <v>25</v>
@@ -1476,46 +1539,46 @@
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="N6" s="2" t="s">
         <v>37</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I6" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J6" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="M6" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="N6" s="2" t="s">
-        <v>34</v>
       </c>
       <c r="O6" s="2" t="s">
         <v>28</v>
@@ -1523,22 +1586,22 @@
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D7" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="G7" s="2" t="s">
         <v>20</v>
@@ -1550,10 +1613,10 @@
         <v>22</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L7" s="2" t="s">
         <v>25</v>
@@ -1562,7 +1625,7 @@
         <v>26</v>
       </c>
       <c r="N7" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O7" s="2" t="s">
         <v>28</v>
@@ -1570,22 +1633,22 @@
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>46</v>
+        <v>49</v>
       </c>
       <c r="G8" s="2" t="s">
         <v>20</v>
@@ -1600,13 +1663,13 @@
         <v>23</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L8" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M8" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N8" s="2" t="s">
         <v>27</v>
@@ -1617,7 +1680,7 @@
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>15</v>
+        <v>50</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>16</v>
@@ -1629,10 +1692,10 @@
         <v>18</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>47</v>
+        <v>51</v>
       </c>
       <c r="G9" s="2" t="s">
         <v>20</v>
@@ -1664,22 +1727,22 @@
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>48</v>
+        <v>52</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D10" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>49</v>
+        <v>53</v>
       </c>
       <c r="G10" s="2" t="s">
         <v>20</v>
@@ -1694,7 +1757,7 @@
         <v>23</v>
       </c>
       <c r="K10" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L10" s="2" t="s">
         <v>25</v>
@@ -1711,22 +1774,22 @@
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>50</v>
+        <v>54</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D11" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>51</v>
+        <v>55</v>
       </c>
       <c r="G11" s="2" t="s">
         <v>20</v>
@@ -1738,10 +1801,10 @@
         <v>22</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K11" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L11" s="2" t="s">
         <v>25</v>
@@ -1750,7 +1813,7 @@
         <v>26</v>
       </c>
       <c r="N11" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O11" s="2" t="s">
         <v>28</v>
@@ -1758,7 +1821,7 @@
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>15</v>
+        <v>57</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>16</v>
@@ -1770,10 +1833,10 @@
         <v>18</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>52</v>
+        <v>58</v>
       </c>
       <c r="G12" s="2" t="s">
         <v>20</v>
@@ -1805,22 +1868,22 @@
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>53</v>
+        <v>59</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D13" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>54</v>
+        <v>60</v>
       </c>
       <c r="G13" s="2" t="s">
         <v>20</v>
@@ -1832,10 +1895,10 @@
         <v>22</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K13" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L13" s="2" t="s">
         <v>25</v>
@@ -1844,7 +1907,7 @@
         <v>26</v>
       </c>
       <c r="N13" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O13" s="2" t="s">
         <v>28</v>
@@ -1852,22 +1915,22 @@
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>56</v>
+        <v>63</v>
       </c>
       <c r="G14" s="2" t="s">
         <v>20</v>
@@ -1879,19 +1942,19 @@
         <v>22</v>
       </c>
       <c r="J14" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K14" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L14" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O14" s="2" t="s">
         <v>28</v>
@@ -1899,22 +1962,22 @@
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="G15" s="2" t="s">
         <v>20</v>
@@ -1929,13 +1992,13 @@
         <v>23</v>
       </c>
       <c r="K15" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L15" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>27</v>
@@ -1946,22 +2009,22 @@
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D16" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="G16" s="2" t="s">
         <v>20</v>
@@ -1976,7 +2039,7 @@
         <v>23</v>
       </c>
       <c r="K16" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L16" s="2" t="s">
         <v>25</v>
@@ -1993,46 +2056,46 @@
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>65</v>
+        <v>71</v>
       </c>
       <c r="G17" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>66</v>
+        <v>21</v>
       </c>
       <c r="I17" s="2" t="s">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="J17" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K17" s="2" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="L17" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M17" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N17" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O17" s="2" t="s">
         <v>28</v>
@@ -2040,22 +2103,22 @@
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>72</v>
+        <v>76</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D18" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>73</v>
+        <v>77</v>
       </c>
       <c r="G18" s="2" t="s">
         <v>20</v>
@@ -2067,63 +2130,63 @@
         <v>22</v>
       </c>
       <c r="J18" s="2" t="s">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="K18" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L18" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M18" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N18" s="2" t="s">
         <v>27</v>
       </c>
       <c r="O18" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>78</v>
+        <v>84</v>
       </c>
       <c r="G19" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I19" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J19" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K19" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L19" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M19" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N19" s="2" t="s">
         <v>27</v>
@@ -2134,22 +2197,22 @@
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="G20" s="2" t="s">
         <v>20</v>
@@ -2161,42 +2224,42 @@
         <v>22</v>
       </c>
       <c r="J20" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K20" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L20" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M20" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N20" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O20" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D21" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>87</v>
+        <v>93</v>
       </c>
       <c r="G21" s="2" t="s">
         <v>20</v>
@@ -2211,10 +2274,10 @@
         <v>23</v>
       </c>
       <c r="K21" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L21" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M21" s="2" t="s">
         <v>26</v>
@@ -2228,22 +2291,22 @@
     </row>
     <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
-        <v>88</v>
+        <v>94</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D22" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E22" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>89</v>
+        <v>95</v>
       </c>
       <c r="G22" s="2" t="s">
         <v>20</v>
@@ -2255,10 +2318,10 @@
         <v>22</v>
       </c>
       <c r="J22" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K22" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L22" s="2" t="s">
         <v>25</v>
@@ -2267,7 +2330,7 @@
         <v>26</v>
       </c>
       <c r="N22" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O22" s="2" t="s">
         <v>28</v>
@@ -2275,22 +2338,22 @@
     </row>
     <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>90</v>
+        <v>96</v>
       </c>
       <c r="B23" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D23" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="G23" s="2" t="s">
         <v>20</v>
@@ -2305,7 +2368,7 @@
         <v>23</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L23" s="2" t="s">
         <v>25</v>
@@ -2322,22 +2385,22 @@
     </row>
     <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>92</v>
+        <v>99</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D24" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>93</v>
+        <v>100</v>
       </c>
       <c r="G24" s="2" t="s">
         <v>20</v>
@@ -2349,19 +2412,19 @@
         <v>22</v>
       </c>
       <c r="J24" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K24" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L24" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M24" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N24" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O24" s="2" t="s">
         <v>28</v>
@@ -2369,22 +2432,22 @@
     </row>
     <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D25" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E25" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>95</v>
+        <v>102</v>
       </c>
       <c r="G25" s="2" t="s">
         <v>20</v>
@@ -2399,7 +2462,7 @@
         <v>23</v>
       </c>
       <c r="K25" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L25" s="2" t="s">
         <v>25</v>
@@ -2416,22 +2479,22 @@
     </row>
     <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>97</v>
+        <v>104</v>
       </c>
       <c r="G26" s="2" t="s">
         <v>20</v>
@@ -2443,10 +2506,10 @@
         <v>22</v>
       </c>
       <c r="J26" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K26" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L26" s="2" t="s">
         <v>25</v>
@@ -2455,7 +2518,7 @@
         <v>26</v>
       </c>
       <c r="N26" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O26" s="2" t="s">
         <v>28</v>
@@ -2463,46 +2526,46 @@
     </row>
     <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
-        <v>99</v>
+        <v>106</v>
       </c>
       <c r="B27" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E27" s="2" t="s">
-        <v>100</v>
+        <v>107</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>101</v>
+        <v>108</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>79</v>
+        <v>85</v>
       </c>
       <c r="I27" s="2" t="s">
-        <v>80</v>
+        <v>86</v>
       </c>
       <c r="J27" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K27" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L27" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M27" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N27" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O27" s="2" t="s">
         <v>28</v>
@@ -2510,25 +2573,25 @@
     </row>
     <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
-        <v>104</v>
+        <v>111</v>
       </c>
       <c r="B28" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D28" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>105</v>
+        <v>112</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H28" s="2" t="s">
         <v>21</v>
@@ -2537,19 +2600,19 @@
         <v>22</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L28" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M28" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N28" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O28" s="2" t="s">
         <v>28</v>
@@ -2557,22 +2620,22 @@
     </row>
     <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>106</v>
+        <v>114</v>
       </c>
       <c r="B29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D29" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E29" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>107</v>
+        <v>115</v>
       </c>
       <c r="G29" s="2" t="s">
         <v>20</v>
@@ -2584,19 +2647,19 @@
         <v>22</v>
       </c>
       <c r="J29" s="2" t="s">
-        <v>98</v>
+        <v>105</v>
       </c>
       <c r="K29" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L29" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M29" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N29" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O29" s="2" t="s">
         <v>28</v>
@@ -2604,22 +2667,22 @@
     </row>
     <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
-        <v>109</v>
+        <v>117</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D30" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E30" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>110</v>
+        <v>118</v>
       </c>
       <c r="G30" s="2" t="s">
         <v>20</v>
@@ -2631,10 +2694,10 @@
         <v>22</v>
       </c>
       <c r="J30" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K30" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L30" s="2" t="s">
         <v>25</v>
@@ -2643,7 +2706,7 @@
         <v>26</v>
       </c>
       <c r="N30" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O30" s="2" t="s">
         <v>28</v>
@@ -2651,22 +2714,22 @@
     </row>
     <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
-        <v>111</v>
+        <v>119</v>
       </c>
       <c r="B31" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D31" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E31" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>112</v>
+        <v>120</v>
       </c>
       <c r="G31" s="2" t="s">
         <v>20</v>
@@ -2678,19 +2741,19 @@
         <v>22</v>
       </c>
       <c r="J31" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K31" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L31" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M31" s="2" t="s">
         <v>26</v>
       </c>
       <c r="N31" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O31" s="2" t="s">
         <v>28</v>
@@ -2698,25 +2761,25 @@
     </row>
     <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
-        <v>113</v>
+        <v>121</v>
       </c>
       <c r="B32" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E32" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>114</v>
+        <v>122</v>
       </c>
       <c r="G32" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H32" s="2" t="s">
         <v>21</v>
@@ -2725,10 +2788,10 @@
         <v>22</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L32" s="2" t="s">
         <v>25</v>
@@ -2737,7 +2800,7 @@
         <v>26</v>
       </c>
       <c r="N32" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O32" s="2" t="s">
         <v>28</v>
@@ -2745,22 +2808,22 @@
     </row>
     <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
-        <v>115</v>
+        <v>123</v>
       </c>
       <c r="B33" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D33" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E33" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>116</v>
+        <v>124</v>
       </c>
       <c r="G33" s="2" t="s">
         <v>20</v>
@@ -2772,19 +2835,19 @@
         <v>22</v>
       </c>
       <c r="J33" s="2" t="s">
-        <v>117</v>
+        <v>125</v>
       </c>
       <c r="K33" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L33" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M33" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N33" s="2" t="s">
-        <v>71</v>
+        <v>75</v>
       </c>
       <c r="O33" s="2" t="s">
         <v>28</v>
@@ -2792,22 +2855,22 @@
     </row>
     <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
-        <v>118</v>
+        <v>126</v>
       </c>
       <c r="B34" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D34" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E34" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>119</v>
+        <v>127</v>
       </c>
       <c r="G34" s="2" t="s">
         <v>20</v>
@@ -2819,10 +2882,10 @@
         <v>22</v>
       </c>
       <c r="J34" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K34" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L34" s="2" t="s">
         <v>25</v>
@@ -2831,7 +2894,7 @@
         <v>26</v>
       </c>
       <c r="N34" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O34" s="2" t="s">
         <v>28</v>
@@ -2839,22 +2902,22 @@
     </row>
     <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
-        <v>120</v>
+        <v>128</v>
       </c>
       <c r="B35" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D35" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E35" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>121</v>
+        <v>129</v>
       </c>
       <c r="G35" s="2" t="s">
         <v>20</v>
@@ -2869,10 +2932,10 @@
         <v>23</v>
       </c>
       <c r="K35" s="2" t="s">
-        <v>24</v>
+        <v>113</v>
       </c>
       <c r="L35" s="2" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="M35" s="2" t="s">
         <v>26</v>
@@ -2886,7 +2949,7 @@
     </row>
     <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
-        <v>15</v>
+        <v>130</v>
       </c>
       <c r="B36" s="2" t="s">
         <v>16</v>
@@ -2898,10 +2961,10 @@
         <v>18</v>
       </c>
       <c r="E36" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>122</v>
+        <v>131</v>
       </c>
       <c r="G36" s="2" t="s">
         <v>20</v>
@@ -2916,7 +2979,7 @@
         <v>23</v>
       </c>
       <c r="K36" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L36" s="2" t="s">
         <v>25</v>
@@ -2933,7 +2996,7 @@
     </row>
     <row r="37" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="B37" s="2" t="s">
         <v>16</v>
@@ -2945,10 +3008,10 @@
         <v>18</v>
       </c>
       <c r="E37" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>123</v>
+        <v>133</v>
       </c>
       <c r="G37" s="2" t="s">
         <v>20</v>
@@ -2963,13 +3026,13 @@
         <v>23</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="L37" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M37" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N37" s="2" t="s">
         <v>27</v>
@@ -2980,22 +3043,22 @@
     </row>
     <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
-        <v>124</v>
+        <v>134</v>
       </c>
       <c r="B38" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E38" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>125</v>
+        <v>135</v>
       </c>
       <c r="G38" s="2" t="s">
         <v>20</v>
@@ -3010,7 +3073,7 @@
         <v>23</v>
       </c>
       <c r="K38" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L38" s="2" t="s">
         <v>25</v>
@@ -3027,22 +3090,22 @@
     </row>
     <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>126</v>
+        <v>136</v>
       </c>
       <c r="B39" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D39" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E39" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="F39" s="2" t="s">
-        <v>127</v>
+        <v>137</v>
       </c>
       <c r="G39" s="2" t="s">
         <v>20</v>
@@ -3054,10 +3117,10 @@
         <v>22</v>
       </c>
       <c r="J39" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L39" s="2" t="s">
         <v>25</v>
@@ -3066,7 +3129,7 @@
         <v>26</v>
       </c>
       <c r="N39" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O39" s="2" t="s">
         <v>28</v>
@@ -3074,22 +3137,22 @@
     </row>
     <row r="40" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
-        <v>128</v>
+        <v>138</v>
       </c>
       <c r="B40" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C40" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D40" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E40" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="F40" s="2" t="s">
-        <v>129</v>
+        <v>139</v>
       </c>
       <c r="G40" s="2" t="s">
         <v>20</v>
@@ -3101,10 +3164,10 @@
         <v>22</v>
       </c>
       <c r="J40" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K40" s="2" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="L40" s="2" t="s">
         <v>25</v>
@@ -3113,7 +3176,7 @@
         <v>26</v>
       </c>
       <c r="N40" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O40" s="2" t="s">
         <v>28</v>
@@ -3121,22 +3184,22 @@
     </row>
     <row r="41" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
-        <v>130</v>
+        <v>141</v>
       </c>
       <c r="B41" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C41" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D41" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E41" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="F41" s="2" t="s">
-        <v>131</v>
+        <v>142</v>
       </c>
       <c r="G41" s="2" t="s">
         <v>20</v>
@@ -3148,10 +3211,10 @@
         <v>22</v>
       </c>
       <c r="J41" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K41" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L41" s="2" t="s">
         <v>25</v>
@@ -3160,7 +3223,7 @@
         <v>26</v>
       </c>
       <c r="N41" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O41" s="2" t="s">
         <v>28</v>
@@ -3168,22 +3231,22 @@
     </row>
     <row r="42" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
-        <v>132</v>
+        <v>143</v>
       </c>
       <c r="B42" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C42" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D42" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E42" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="F42" s="2" t="s">
-        <v>133</v>
+        <v>144</v>
       </c>
       <c r="G42" s="2" t="s">
         <v>20</v>
@@ -3198,7 +3261,7 @@
         <v>23</v>
       </c>
       <c r="K42" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L42" s="2" t="s">
         <v>25</v>
@@ -3215,25 +3278,25 @@
     </row>
     <row r="43" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>134</v>
+        <v>145</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C43" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D43" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E43" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="F43" s="2" t="s">
-        <v>135</v>
+        <v>146</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H43" s="2" t="s">
         <v>21</v>
@@ -3242,10 +3305,10 @@
         <v>22</v>
       </c>
       <c r="J43" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K43" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L43" s="2" t="s">
         <v>25</v>
@@ -3254,30 +3317,30 @@
         <v>26</v>
       </c>
       <c r="N43" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O43" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
-        <v>136</v>
+        <v>147</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C44" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D44" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E44" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="F44" s="2" t="s">
-        <v>137</v>
+        <v>148</v>
       </c>
       <c r="G44" s="2" t="s">
         <v>20</v>
@@ -3292,7 +3355,7 @@
         <v>23</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L44" s="2" t="s">
         <v>25</v>
@@ -3309,46 +3372,46 @@
     </row>
     <row r="45" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
-        <v>138</v>
+        <v>149</v>
       </c>
       <c r="B45" s="2" t="s">
-        <v>16</v>
+        <v>150</v>
       </c>
       <c r="C45" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E45" s="2" t="s">
-        <v>139</v>
+        <v>151</v>
       </c>
       <c r="F45" s="2" t="s">
-        <v>140</v>
+        <v>152</v>
       </c>
       <c r="G45" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H45" s="2" t="s">
-        <v>141</v>
+        <v>153</v>
       </c>
       <c r="I45" s="2" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="J45" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K45" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L45" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M45" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N45" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O45" s="2" t="s">
         <v>28</v>
@@ -3356,38 +3419,38 @@
     </row>
     <row r="46" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
-        <v>142</v>
+        <v>155</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C46" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="F46" s="2" t="s">
+        <v>156</v>
+      </c>
+      <c r="G46" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H46" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I46" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J46" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K46" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D46" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="F46" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="G46" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H46" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J46" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K46" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L46" s="2" t="s">
         <v>25</v>
       </c>
@@ -3395,7 +3458,7 @@
         <v>26</v>
       </c>
       <c r="N46" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O46" s="2" t="s">
         <v>28</v>
@@ -3403,22 +3466,22 @@
     </row>
     <row r="47" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
-        <v>144</v>
+        <v>157</v>
       </c>
       <c r="B47" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C47" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D47" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="F47" s="2" t="s">
-        <v>145</v>
+        <v>158</v>
       </c>
       <c r="G47" s="2" t="s">
         <v>20</v>
@@ -3430,10 +3493,10 @@
         <v>22</v>
       </c>
       <c r="J47" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K47" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L47" s="2" t="s">
         <v>25</v>
@@ -3442,7 +3505,7 @@
         <v>26</v>
       </c>
       <c r="N47" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O47" s="2" t="s">
         <v>28</v>
@@ -3450,22 +3513,22 @@
     </row>
     <row r="48" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
-        <v>146</v>
+        <v>159</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C48" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="F48" s="2" t="s">
-        <v>147</v>
+        <v>160</v>
       </c>
       <c r="G48" s="2" t="s">
         <v>20</v>
@@ -3477,10 +3540,10 @@
         <v>22</v>
       </c>
       <c r="J48" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K48" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L48" s="2" t="s">
         <v>25</v>
@@ -3489,7 +3552,7 @@
         <v>26</v>
       </c>
       <c r="N48" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O48" s="2" t="s">
         <v>28</v>
@@ -3497,22 +3560,22 @@
     </row>
     <row r="49" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
-        <v>148</v>
+        <v>161</v>
       </c>
       <c r="B49" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C49" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="F49" s="2" t="s">
-        <v>149</v>
+        <v>162</v>
       </c>
       <c r="G49" s="2" t="s">
         <v>20</v>
@@ -3524,10 +3587,10 @@
         <v>22</v>
       </c>
       <c r="J49" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K49" s="2" t="s">
-        <v>24</v>
+        <v>36</v>
       </c>
       <c r="L49" s="2" t="s">
         <v>25</v>
@@ -3536,7 +3599,7 @@
         <v>26</v>
       </c>
       <c r="N49" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O49" s="2" t="s">
         <v>28</v>
@@ -3544,22 +3607,22 @@
     </row>
     <row r="50" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>150</v>
+        <v>163</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E50" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="F50" s="2" t="s">
-        <v>151</v>
+        <v>164</v>
       </c>
       <c r="G50" s="2" t="s">
         <v>20</v>
@@ -3571,10 +3634,10 @@
         <v>22</v>
       </c>
       <c r="J50" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K50" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L50" s="2" t="s">
         <v>25</v>
@@ -3583,7 +3646,7 @@
         <v>26</v>
       </c>
       <c r="N50" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O50" s="2" t="s">
         <v>28</v>
@@ -3591,22 +3654,22 @@
     </row>
     <row r="51" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C51" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E51" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="F51" s="2" t="s">
-        <v>153</v>
+        <v>166</v>
       </c>
       <c r="G51" s="2" t="s">
         <v>20</v>
@@ -3618,10 +3681,10 @@
         <v>22</v>
       </c>
       <c r="J51" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K51" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L51" s="2" t="s">
         <v>25</v>
@@ -3630,7 +3693,7 @@
         <v>26</v>
       </c>
       <c r="N51" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O51" s="2" t="s">
         <v>28</v>
@@ -3638,22 +3701,22 @@
     </row>
     <row r="52" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
-        <v>154</v>
+        <v>167</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C52" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E52" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="F52" s="2" t="s">
-        <v>155</v>
+        <v>168</v>
       </c>
       <c r="G52" s="2" t="s">
         <v>20</v>
@@ -3668,7 +3731,7 @@
         <v>23</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L52" s="2" t="s">
         <v>25</v>
@@ -3685,22 +3748,22 @@
     </row>
     <row r="53" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>156</v>
+        <v>169</v>
       </c>
       <c r="B53" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D53" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E53" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="F53" s="2" t="s">
-        <v>157</v>
+        <v>170</v>
       </c>
       <c r="G53" s="2" t="s">
         <v>20</v>
@@ -3715,7 +3778,7 @@
         <v>23</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>24</v>
+        <v>98</v>
       </c>
       <c r="L53" s="2" t="s">
         <v>25</v>
@@ -3732,22 +3795,22 @@
     </row>
     <row r="54" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
-        <v>158</v>
+        <v>171</v>
       </c>
       <c r="B54" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C54" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D54" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E54" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="F54" s="2" t="s">
-        <v>159</v>
+        <v>172</v>
       </c>
       <c r="G54" s="2" t="s">
         <v>20</v>
@@ -3759,19 +3822,19 @@
         <v>22</v>
       </c>
       <c r="J54" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K54" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L54" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M54" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N54" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O54" s="2" t="s">
         <v>28</v>
@@ -3779,25 +3842,25 @@
     </row>
     <row r="55" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
-        <v>160</v>
+        <v>173</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C55" s="2" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="D55" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E55" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="F55" s="2" t="s">
-        <v>161</v>
+        <v>174</v>
       </c>
       <c r="G55" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H55" s="2" t="s">
         <v>21</v>
@@ -3809,13 +3872,13 @@
         <v>23</v>
       </c>
       <c r="K55" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L55" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M55" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N55" s="2" t="s">
         <v>27</v>
@@ -3826,22 +3889,22 @@
     </row>
     <row r="56" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>162</v>
+        <v>175</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D56" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E56" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="F56" s="2" t="s">
-        <v>163</v>
+        <v>176</v>
       </c>
       <c r="G56" s="2" t="s">
         <v>20</v>
@@ -3853,10 +3916,10 @@
         <v>22</v>
       </c>
       <c r="J56" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L56" s="2" t="s">
         <v>25</v>
@@ -3865,7 +3928,7 @@
         <v>26</v>
       </c>
       <c r="N56" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O56" s="2" t="s">
         <v>28</v>
@@ -3873,22 +3936,22 @@
     </row>
     <row r="57" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
-        <v>164</v>
+        <v>177</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C57" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D57" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E57" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="F57" s="2" t="s">
-        <v>165</v>
+        <v>178</v>
       </c>
       <c r="G57" s="2" t="s">
         <v>20</v>
@@ -3900,10 +3963,10 @@
         <v>22</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L57" s="2" t="s">
         <v>25</v>
@@ -3912,7 +3975,7 @@
         <v>26</v>
       </c>
       <c r="N57" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O57" s="2" t="s">
         <v>28</v>
@@ -3920,38 +3983,38 @@
     </row>
     <row r="58" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
-        <v>166</v>
+        <v>179</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C58" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D58" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="F58" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="G58" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="H58" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="I58" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="J58" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="K58" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D58" s="2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E58" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="G58" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="H58" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="I58" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="J58" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="K58" s="2" t="s">
-        <v>24</v>
-      </c>
       <c r="L58" s="2" t="s">
         <v>25</v>
       </c>
@@ -3959,7 +4022,7 @@
         <v>26</v>
       </c>
       <c r="N58" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O58" s="2" t="s">
         <v>28</v>
@@ -3967,22 +4030,22 @@
     </row>
     <row r="59" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>168</v>
+        <v>181</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E59" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="F59" s="2" t="s">
-        <v>169</v>
+        <v>182</v>
       </c>
       <c r="G59" s="2" t="s">
         <v>20</v>
@@ -3994,10 +4057,10 @@
         <v>22</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L59" s="2" t="s">
         <v>25</v>
@@ -4006,7 +4069,7 @@
         <v>26</v>
       </c>
       <c r="N59" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O59" s="2" t="s">
         <v>28</v>
@@ -4014,22 +4077,22 @@
     </row>
     <row r="60" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
-        <v>170</v>
+        <v>183</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E60" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="F60" s="2" t="s">
-        <v>171</v>
+        <v>184</v>
       </c>
       <c r="G60" s="2" t="s">
         <v>20</v>
@@ -4041,10 +4104,10 @@
         <v>22</v>
       </c>
       <c r="J60" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K60" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L60" s="2" t="s">
         <v>25</v>
@@ -4053,7 +4116,7 @@
         <v>26</v>
       </c>
       <c r="N60" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O60" s="2" t="s">
         <v>28</v>
@@ -4061,25 +4124,25 @@
     </row>
     <row r="61" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
-        <v>172</v>
+        <v>185</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C61" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E61" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="F61" s="2" t="s">
-        <v>173</v>
+        <v>186</v>
       </c>
       <c r="G61" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H61" s="2" t="s">
         <v>21</v>
@@ -4088,10 +4151,10 @@
         <v>22</v>
       </c>
       <c r="J61" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K61" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L61" s="2" t="s">
         <v>25</v>
@@ -4100,7 +4163,7 @@
         <v>26</v>
       </c>
       <c r="N61" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O61" s="2" t="s">
         <v>28</v>
@@ -4108,22 +4171,22 @@
     </row>
     <row r="62" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
-        <v>174</v>
+        <v>187</v>
       </c>
       <c r="B62" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="F62" s="2" t="s">
-        <v>175</v>
+        <v>188</v>
       </c>
       <c r="G62" s="2" t="s">
         <v>20</v>
@@ -4135,19 +4198,19 @@
         <v>22</v>
       </c>
       <c r="J62" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K62" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L62" s="2" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="M62" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N62" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O62" s="2" t="s">
         <v>28</v>
@@ -4155,22 +4218,22 @@
     </row>
     <row r="63" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
-        <v>176</v>
+        <v>189</v>
       </c>
       <c r="B63" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D63" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E63" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="F63" s="2" t="s">
-        <v>177</v>
+        <v>190</v>
       </c>
       <c r="G63" s="2" t="s">
         <v>20</v>
@@ -4185,13 +4248,13 @@
         <v>23</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L63" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M63" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N63" s="2" t="s">
         <v>27</v>
@@ -4202,22 +4265,22 @@
     </row>
     <row r="64" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
-        <v>178</v>
+        <v>191</v>
       </c>
       <c r="B64" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D64" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E64" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="F64" s="2" t="s">
-        <v>179</v>
+        <v>192</v>
       </c>
       <c r="G64" s="2" t="s">
         <v>20</v>
@@ -4232,7 +4295,7 @@
         <v>23</v>
       </c>
       <c r="K64" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L64" s="2" t="s">
         <v>25</v>
@@ -4249,22 +4312,22 @@
     </row>
     <row r="65" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
-        <v>180</v>
+        <v>193</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C65" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D65" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E65" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="F65" s="2" t="s">
-        <v>181</v>
+        <v>194</v>
       </c>
       <c r="G65" s="2" t="s">
         <v>20</v>
@@ -4279,7 +4342,7 @@
         <v>23</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L65" s="2" t="s">
         <v>25</v>
@@ -4296,22 +4359,22 @@
     </row>
     <row r="66" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>182</v>
+        <v>195</v>
       </c>
       <c r="B66" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D66" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="F66" s="2" t="s">
-        <v>183</v>
+        <v>196</v>
       </c>
       <c r="G66" s="2" t="s">
         <v>20</v>
@@ -4326,7 +4389,7 @@
         <v>23</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L66" s="2" t="s">
         <v>25</v>
@@ -4343,22 +4406,22 @@
     </row>
     <row r="67" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
-        <v>184</v>
+        <v>197</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D67" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E67" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="F67" s="2" t="s">
-        <v>185</v>
+        <v>198</v>
       </c>
       <c r="G67" s="2" t="s">
         <v>20</v>
@@ -4370,10 +4433,10 @@
         <v>22</v>
       </c>
       <c r="J67" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K67" s="2" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="L67" s="2" t="s">
         <v>25</v>
@@ -4382,7 +4445,7 @@
         <v>26</v>
       </c>
       <c r="N67" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O67" s="2" t="s">
         <v>28</v>
@@ -4390,25 +4453,25 @@
     </row>
     <row r="68" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D68" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E68" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="F68" s="2" t="s">
-        <v>187</v>
+        <v>200</v>
       </c>
       <c r="G68" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H68" s="2" t="s">
         <v>21</v>
@@ -4417,19 +4480,19 @@
         <v>22</v>
       </c>
       <c r="J68" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K68" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L68" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M68" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N68" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O68" s="2" t="s">
         <v>28</v>
@@ -4437,37 +4500,37 @@
     </row>
     <row r="69" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>16</v>
+        <v>202</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E69" s="2" t="s">
-        <v>189</v>
+        <v>203</v>
       </c>
       <c r="F69" s="2" t="s">
-        <v>190</v>
+        <v>204</v>
       </c>
       <c r="G69" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H69" s="2" t="s">
-        <v>191</v>
+        <v>205</v>
       </c>
       <c r="I69" s="2" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="J69" s="2" t="s">
         <v>23</v>
       </c>
       <c r="K69" s="2" t="s">
-        <v>81</v>
+        <v>87</v>
       </c>
       <c r="L69" s="2" t="s">
         <v>25</v>
@@ -4484,22 +4547,22 @@
     </row>
     <row r="70" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
-        <v>192</v>
+        <v>206</v>
       </c>
       <c r="B70" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D70" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="F70" s="2" t="s">
-        <v>193</v>
+        <v>207</v>
       </c>
       <c r="G70" s="2" t="s">
         <v>20</v>
@@ -4514,13 +4577,13 @@
         <v>23</v>
       </c>
       <c r="K70" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L70" s="2" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="M70" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N70" s="2" t="s">
         <v>27</v>
@@ -4531,25 +4594,25 @@
     </row>
     <row r="71" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
-        <v>194</v>
+        <v>208</v>
       </c>
       <c r="B71" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D71" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E71" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="F71" s="2" t="s">
-        <v>195</v>
+        <v>209</v>
       </c>
       <c r="G71" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H71" s="2" t="s">
         <v>21</v>
@@ -4561,7 +4624,7 @@
         <v>23</v>
       </c>
       <c r="K71" s="2" t="s">
-        <v>24</v>
+        <v>140</v>
       </c>
       <c r="L71" s="2" t="s">
         <v>25</v>
@@ -4578,22 +4641,22 @@
     </row>
     <row r="72" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
-        <v>196</v>
+        <v>210</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D72" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E72" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="F72" s="2" t="s">
-        <v>197</v>
+        <v>211</v>
       </c>
       <c r="G72" s="2" t="s">
         <v>20</v>
@@ -4605,10 +4668,10 @@
         <v>22</v>
       </c>
       <c r="J72" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K72" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L72" s="2" t="s">
         <v>25</v>
@@ -4617,7 +4680,7 @@
         <v>26</v>
       </c>
       <c r="N72" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O72" s="2" t="s">
         <v>28</v>
@@ -4625,22 +4688,22 @@
     </row>
     <row r="73" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
-        <v>198</v>
+        <v>212</v>
       </c>
       <c r="B73" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D73" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="F73" s="2" t="s">
-        <v>199</v>
+        <v>213</v>
       </c>
       <c r="G73" s="2" t="s">
         <v>20</v>
@@ -4652,10 +4715,10 @@
         <v>22</v>
       </c>
       <c r="J73" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K73" s="2" t="s">
-        <v>24</v>
+        <v>56</v>
       </c>
       <c r="L73" s="2" t="s">
         <v>25</v>
@@ -4664,7 +4727,7 @@
         <v>26</v>
       </c>
       <c r="N73" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O73" s="2" t="s">
         <v>28</v>
@@ -4672,22 +4735,22 @@
     </row>
     <row r="74" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
-        <v>200</v>
+        <v>214</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D74" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E74" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="F74" s="2" t="s">
-        <v>201</v>
+        <v>215</v>
       </c>
       <c r="G74" s="2" t="s">
         <v>20</v>
@@ -4699,10 +4762,10 @@
         <v>22</v>
       </c>
       <c r="J74" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K74" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L74" s="2" t="s">
         <v>25</v>
@@ -4711,7 +4774,7 @@
         <v>26</v>
       </c>
       <c r="N74" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O74" s="2" t="s">
         <v>28</v>
@@ -4719,37 +4782,37 @@
     </row>
     <row r="75" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
-        <v>202</v>
+        <v>216</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>63</v>
+        <v>18</v>
       </c>
       <c r="E75" s="2" t="s">
-        <v>204</v>
+        <v>217</v>
       </c>
       <c r="F75" s="2" t="s">
-        <v>205</v>
+        <v>217</v>
       </c>
       <c r="G75" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H75" s="2" t="s">
-        <v>206</v>
+        <v>21</v>
       </c>
       <c r="I75" s="2" t="s">
-        <v>80</v>
+        <v>22</v>
       </c>
       <c r="J75" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K75" s="2" t="s">
-        <v>207</v>
+        <v>56</v>
       </c>
       <c r="L75" s="2" t="s">
         <v>25</v>
@@ -4758,7 +4821,7 @@
         <v>26</v>
       </c>
       <c r="N75" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O75" s="2" t="s">
         <v>28</v>
@@ -4766,22 +4829,22 @@
     </row>
     <row r="76" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
-        <v>192</v>
+        <v>218</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D76" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E76" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="F76" s="2" t="s">
-        <v>208</v>
+        <v>219</v>
       </c>
       <c r="G76" s="2" t="s">
         <v>20</v>
@@ -4793,10 +4856,10 @@
         <v>22</v>
       </c>
       <c r="J76" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K76" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L76" s="2" t="s">
         <v>25</v>
@@ -4805,7 +4868,7 @@
         <v>26</v>
       </c>
       <c r="N76" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O76" s="2" t="s">
         <v>28</v>
@@ -4813,25 +4876,25 @@
     </row>
     <row r="77" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
-        <v>186</v>
+        <v>220</v>
       </c>
       <c r="B77" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C77" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D77" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E77" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="F77" s="2" t="s">
-        <v>209</v>
+        <v>221</v>
       </c>
       <c r="G77" s="2" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H77" s="2" t="s">
         <v>21</v>
@@ -4843,7 +4906,7 @@
         <v>23</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L77" s="2" t="s">
         <v>25</v>
@@ -4860,22 +4923,22 @@
     </row>
     <row r="78" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>210</v>
+        <v>222</v>
       </c>
       <c r="B78" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D78" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E78" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="F78" s="2" t="s">
-        <v>211</v>
+        <v>223</v>
       </c>
       <c r="G78" s="2" t="s">
         <v>20</v>
@@ -4907,22 +4970,22 @@
     </row>
     <row r="79" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>212</v>
+        <v>224</v>
       </c>
       <c r="B79" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D79" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E79" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="F79" s="2" t="s">
-        <v>213</v>
+        <v>225</v>
       </c>
       <c r="G79" s="2" t="s">
         <v>20</v>
@@ -4937,13 +5000,13 @@
         <v>23</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>24</v>
+        <v>43</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M79" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N79" s="2" t="s">
         <v>27</v>
@@ -4954,22 +5017,22 @@
     </row>
     <row r="80" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
-        <v>214</v>
+        <v>226</v>
       </c>
       <c r="B80" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C80" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D80" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E80" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="F80" s="2" t="s">
-        <v>215</v>
+        <v>227</v>
       </c>
       <c r="G80" s="2" t="s">
         <v>20</v>
@@ -4984,13 +5047,13 @@
         <v>23</v>
       </c>
       <c r="K80" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L80" s="2" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="M80" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N80" s="2" t="s">
         <v>27</v>
@@ -5001,46 +5064,46 @@
     </row>
     <row r="81" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
-        <v>216</v>
+        <v>228</v>
       </c>
       <c r="B81" s="2" t="s">
-        <v>16</v>
+        <v>229</v>
       </c>
       <c r="C81" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>63</v>
+        <v>82</v>
       </c>
       <c r="E81" s="2" t="s">
-        <v>217</v>
+        <v>230</v>
       </c>
       <c r="F81" s="2" t="s">
-        <v>218</v>
+        <v>231</v>
       </c>
       <c r="G81" s="2" t="s">
         <v>20</v>
       </c>
       <c r="H81" s="2" t="s">
-        <v>219</v>
+        <v>232</v>
       </c>
       <c r="I81" s="2" t="s">
-        <v>67</v>
+        <v>154</v>
       </c>
       <c r="J81" s="2" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="K81" s="2" t="s">
-        <v>220</v>
+        <v>233</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="M81" s="2" t="s">
-        <v>41</v>
+        <v>26</v>
       </c>
       <c r="N81" s="2" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="O81" s="2" t="s">
         <v>28</v>
@@ -5048,22 +5111,22 @@
     </row>
     <row r="82" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
-        <v>180</v>
+        <v>234</v>
       </c>
       <c r="B82" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C82" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D82" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E82" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="F82" s="2" t="s">
-        <v>221</v>
+        <v>235</v>
       </c>
       <c r="G82" s="2" t="s">
         <v>20</v>
@@ -5075,10 +5138,10 @@
         <v>22</v>
       </c>
       <c r="J82" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K82" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L82" s="2" t="s">
         <v>25</v>
@@ -5095,22 +5158,22 @@
     </row>
     <row r="83" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
-        <v>180</v>
+        <v>236</v>
       </c>
       <c r="B83" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C83" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D83" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E83" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="F83" s="2" t="s">
-        <v>223</v>
+        <v>237</v>
       </c>
       <c r="G83" s="2" t="s">
         <v>20</v>
@@ -5122,10 +5185,10 @@
         <v>22</v>
       </c>
       <c r="J83" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K83" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L83" s="2" t="s">
         <v>25</v>
@@ -5142,22 +5205,22 @@
     </row>
     <row r="84" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
-        <v>180</v>
+        <v>238</v>
       </c>
       <c r="B84" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C84" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D84" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E84" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="F84" s="2" t="s">
-        <v>224</v>
+        <v>239</v>
       </c>
       <c r="G84" s="2" t="s">
         <v>20</v>
@@ -5169,10 +5232,10 @@
         <v>22</v>
       </c>
       <c r="J84" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K84" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L84" s="2" t="s">
         <v>25</v>
@@ -5189,22 +5252,22 @@
     </row>
     <row r="85" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
-        <v>180</v>
+        <v>240</v>
       </c>
       <c r="B85" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C85" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D85" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E85" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="F85" s="2" t="s">
-        <v>225</v>
+        <v>241</v>
       </c>
       <c r="G85" s="2" t="s">
         <v>20</v>
@@ -5216,10 +5279,10 @@
         <v>22</v>
       </c>
       <c r="J85" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K85" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L85" s="2" t="s">
         <v>25</v>
@@ -5236,22 +5299,22 @@
     </row>
     <row r="86" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
-        <v>180</v>
+        <v>242</v>
       </c>
       <c r="B86" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C86" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D86" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E86" s="2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="F86" s="2" t="s">
-        <v>226</v>
+        <v>243</v>
       </c>
       <c r="G86" s="2" t="s">
         <v>20</v>
@@ -5263,10 +5326,10 @@
         <v>22</v>
       </c>
       <c r="J86" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K86" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L86" s="2" t="s">
         <v>25</v>
@@ -5283,22 +5346,22 @@
     </row>
     <row r="87" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
-        <v>180</v>
+        <v>244</v>
       </c>
       <c r="B87" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C87" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D87" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E87" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="F87" s="2" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="G87" s="2" t="s">
         <v>20</v>
@@ -5310,10 +5373,10 @@
         <v>22</v>
       </c>
       <c r="J87" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K87" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L87" s="2" t="s">
         <v>25</v>
@@ -5330,22 +5393,22 @@
     </row>
     <row r="88" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
-        <v>180</v>
+        <v>246</v>
       </c>
       <c r="B88" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C88" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D88" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E88" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="F88" s="2" t="s">
-        <v>228</v>
+        <v>247</v>
       </c>
       <c r="G88" s="2" t="s">
         <v>20</v>
@@ -5357,10 +5420,10 @@
         <v>22</v>
       </c>
       <c r="J88" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K88" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L88" s="2" t="s">
         <v>25</v>
@@ -5377,22 +5440,22 @@
     </row>
     <row r="89" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
-        <v>180</v>
+        <v>248</v>
       </c>
       <c r="B89" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C89" s="2" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="D89" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E89" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="F89" s="2" t="s">
-        <v>229</v>
+        <v>249</v>
       </c>
       <c r="G89" s="2" t="s">
         <v>20</v>
@@ -5404,10 +5467,10 @@
         <v>22</v>
       </c>
       <c r="J89" s="2" t="s">
-        <v>222</v>
+        <v>61</v>
       </c>
       <c r="K89" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L89" s="2" t="s">
         <v>25</v>
@@ -5424,22 +5487,22 @@
     </row>
     <row r="90" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
-        <v>230</v>
+        <v>250</v>
       </c>
       <c r="B90" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C90" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D90" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E90" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="F90" s="2" t="s">
-        <v>231</v>
+        <v>251</v>
       </c>
       <c r="G90" s="2" t="s">
         <v>20</v>
@@ -5451,10 +5514,10 @@
         <v>22</v>
       </c>
       <c r="J90" s="2" t="s">
-        <v>232</v>
+        <v>252</v>
       </c>
       <c r="K90" s="2" t="s">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="L90" s="2" t="s">
         <v>25</v>
@@ -5471,22 +5534,22 @@
     </row>
     <row r="91" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
-        <v>233</v>
+        <v>253</v>
       </c>
       <c r="B91" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C91" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D91" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="F91" s="2" t="s">
-        <v>234</v>
+        <v>254</v>
       </c>
       <c r="G91" s="2" t="s">
         <v>20</v>
@@ -5498,10 +5561,10 @@
         <v>22</v>
       </c>
       <c r="J91" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K91" s="2" t="s">
-        <v>24</v>
+        <v>73</v>
       </c>
       <c r="L91" s="2" t="s">
         <v>25</v>
@@ -5510,30 +5573,30 @@
         <v>26</v>
       </c>
       <c r="N91" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O91" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
     <row r="92" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
-        <v>235</v>
+        <v>255</v>
       </c>
       <c r="B92" s="2" t="s">
         <v>16</v>
       </c>
       <c r="C92" s="2" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D92" s="2" t="s">
         <v>18</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="F92" s="2" t="s">
-        <v>236</v>
+        <v>256</v>
       </c>
       <c r="G92" s="2" t="s">
         <v>20</v>
@@ -5545,10 +5608,10 @@
         <v>22</v>
       </c>
       <c r="J92" s="2" t="s">
-        <v>84</v>
+        <v>90</v>
       </c>
       <c r="K92" s="2" t="s">
-        <v>24</v>
+        <v>66</v>
       </c>
       <c r="L92" s="2" t="s">
         <v>25</v>
@@ -5557,10 +5620,10 @@
         <v>26</v>
       </c>
       <c r="N92" s="2" t="s">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="O92" s="2" t="s">
-        <v>75</v>
+        <v>79</v>
       </c>
     </row>
   </sheetData>
@@ -5576,23 +5639,23 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
-        <v>237</v>
+        <v>257</v>
       </c>
       <c r="B1" s="3"/>
       <c r="C1" s="3"/>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>238</v>
+        <v>258</v>
       </c>
       <c r="B2" t="s">
-        <v>239</v>
+        <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="E2" t="s">
-        <v>241</v>
+        <v>261</v>
       </c>
       <c r="F2"/>
       <c r="G2"/>
@@ -5600,16 +5663,16 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>243</v>
+        <v>263</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>244</v>
+        <v>264</v>
       </c>
       <c r="J4" s="1" t="s">
-        <v>245</v>
+        <v>265</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -5620,15 +5683,15 @@
         <v>0</v>
       </c>
       <c r="G5" s="4">
-        <v>295</v>
+        <v>14.53</v>
       </c>
       <c r="J5" s="4">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="21" spans="10:10" x14ac:dyDescent="0.25">
       <c r="J21" s="6" t="s">
-        <v>246</v>
+        <v>266</v>
       </c>
     </row>
     <row r="22" spans="10:11" x14ac:dyDescent="0.25">
@@ -5641,7 +5704,7 @@
     </row>
     <row r="23" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J23" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="K23">
         <v>6</v>
@@ -5649,7 +5712,7 @@
     </row>
     <row r="24" spans="10:11" x14ac:dyDescent="0.25">
       <c r="J24" t="s">
-        <v>247</v>
+        <v>267</v>
       </c>
       <c r="K24">
         <v>0</v>
@@ -5680,12 +5743,12 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>248</v>
+        <v>268</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>242</v>
+        <v>262</v>
       </c>
       <c r="B2">
         <v>91</v>
@@ -5699,35 +5762,35 @@
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6">
-        <v>295</v>
+        <v>14.53</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="6" t="s">
-        <v>249</v>
+        <v>269</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>250</v>
+        <v>270</v>
       </c>
       <c r="G9" s="6" t="s">
         <v>6</v>
       </c>
       <c r="J9" s="6" t="s">
-        <v>251</v>
+        <v>271</v>
       </c>
       <c r="M9" s="6" t="s">
-        <v>252</v>
+        <v>272</v>
       </c>
       <c r="P9" s="6" t="s">
-        <v>253</v>
+        <v>273</v>
       </c>
       <c r="Q9" s="6" t="s">
-        <v>254</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
@@ -5735,22 +5798,22 @@
         <v>16</v>
       </c>
       <c r="B10">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E10">
         <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>255</v>
+        <v>275</v>
       </c>
       <c r="H10">
         <v>0</v>
       </c>
       <c r="J10" t="s">
-        <v>256</v>
+        <v>276</v>
       </c>
       <c r="K10">
         <v>0</v>
@@ -5762,27 +5825,27 @@
         <v>64</v>
       </c>
       <c r="P10" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="Q10">
-        <v>3</v>
+        <v>29</v>
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>203</v>
+        <v>81</v>
       </c>
       <c r="B11">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D11" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="E11">
         <v>19</v>
       </c>
       <c r="G11" t="s">
-        <v>102</v>
+        <v>109</v>
       </c>
       <c r="H11">
         <v>10</v>
@@ -5791,22 +5854,28 @@
         <v>26</v>
       </c>
       <c r="K11">
-        <v>70</v>
+        <v>91</v>
       </c>
       <c r="M11" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="N11">
         <v>12</v>
       </c>
       <c r="P11" t="s">
-        <v>34</v>
+        <v>277</v>
       </c>
       <c r="Q11">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="12" spans="4:17" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="12" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>150</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
       <c r="D12" t="s">
         <v>17</v>
       </c>
@@ -5820,59 +5889,65 @@
         <v>81</v>
       </c>
       <c r="J12" t="s">
-        <v>257</v>
+        <v>278</v>
       </c>
       <c r="K12">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="M12" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="N12">
         <v>2</v>
       </c>
       <c r="P12" t="s">
-        <v>27</v>
+        <v>91</v>
       </c>
       <c r="Q12">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="13" spans="4:17" x14ac:dyDescent="0.25">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>202</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
       <c r="D13" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
       <c r="E13">
         <v>2</v>
       </c>
       <c r="G13" t="s">
-        <v>258</v>
+        <v>279</v>
       </c>
       <c r="H13">
         <v>0</v>
       </c>
       <c r="M13" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="N13">
         <v>4</v>
       </c>
-      <c r="P13" t="s">
-        <v>85</v>
-      </c>
-      <c r="Q13">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="7:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>229</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
       <c r="G14" t="s">
-        <v>259</v>
+        <v>280</v>
       </c>
       <c r="H14">
         <v>0</v>
       </c>
       <c r="M14" t="s">
-        <v>70</v>
+        <v>74</v>
       </c>
       <c r="N14">
         <v>6</v>
@@ -5880,7 +5955,7 @@
     </row>
     <row r="15" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M15" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
       <c r="N15">
         <v>3</v>
@@ -5888,7 +5963,7 @@
     </row>
     <row r="16" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M16" t="s">
-        <v>260</v>
+        <v>281</v>
       </c>
       <c r="N16">
         <v>0</v>
@@ -5896,7 +5971,7 @@
     </row>
     <row r="17" spans="13:14" x14ac:dyDescent="0.25">
       <c r="M17" t="s">
-        <v>261</v>
+        <v>282</v>
       </c>
       <c r="N17">
         <v>0</v>
@@ -5904,10 +5979,10 @@
     </row>
     <row r="19" spans="4:4" x14ac:dyDescent="0.25">
       <c r="D19" s="6" t="s">
-        <v>262</v>
-      </c>
-    </row>
-    <row r="20" ht="18" customHeight="1" spans="4:7" x14ac:dyDescent="0.25">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="20" spans="4:7" x14ac:dyDescent="0.25">
       <c r="D20" s="1" t="s">
         <v>0</v>
       </c>
@@ -5915,7 +5990,7 @@
         <v>1</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>263</v>
+        <v>284</v>
       </c>
       <c r="G20" s="1" t="s">
         <v>4</v>
@@ -5923,142 +5998,142 @@
     </row>
     <row r="21" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D21" s="2" t="s">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="E21" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F21" s="2">
-        <v>323</v>
+        <v>383</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>189</v>
+        <v>42</v>
       </c>
     </row>
     <row r="22" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D22" s="2" t="s">
-        <v>62</v>
+        <v>48</v>
       </c>
       <c r="E22" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F22" s="2">
-        <v>266</v>
+        <v>383</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>64</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D23" s="2" t="s">
-        <v>202</v>
+        <v>62</v>
       </c>
       <c r="E23" s="2" t="s">
-        <v>203</v>
+        <v>16</v>
       </c>
       <c r="F23" s="2">
-        <v>251</v>
+        <v>383</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>204</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D24" s="2" t="s">
-        <v>15</v>
+        <v>64</v>
       </c>
       <c r="E24" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F24" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>19</v>
+        <v>65</v>
       </c>
     </row>
     <row r="25" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D25" s="2" t="s">
-        <v>15</v>
+        <v>76</v>
       </c>
       <c r="E25" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F25" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>29</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D26" s="2" t="s">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="F26" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>32</v>
+        <v>83</v>
       </c>
     </row>
     <row r="27" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D27" s="2" t="s">
-        <v>35</v>
+        <v>88</v>
       </c>
       <c r="E27" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F27" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>36</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D28" s="2" t="s">
-        <v>42</v>
+        <v>106</v>
       </c>
       <c r="E28" s="2" t="s">
-        <v>16</v>
+        <v>81</v>
       </c>
       <c r="F28" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G28" s="2" t="s">
-        <v>44</v>
+        <v>107</v>
       </c>
     </row>
     <row r="29" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D29" s="2" t="s">
-        <v>15</v>
+        <v>114</v>
       </c>
       <c r="E29" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F29" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G29" s="2" t="s">
-        <v>47</v>
+        <v>115</v>
       </c>
     </row>
     <row r="30" spans="4:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="D30" s="2" t="s">
-        <v>48</v>
+        <v>123</v>
       </c>
       <c r="E30" s="2" t="s">
         <v>16</v>
       </c>
       <c r="F30" s="2">
-        <v>0</v>
+        <v>383</v>
       </c>
       <c r="G30" s="2" t="s">
-        <v>49</v>
+        <v>124</v>
       </c>
     </row>
   </sheetData>
